--- a/data/raw/market_data2.xlsx
+++ b/data/raw/market_data2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb062ef0b6093a44/Documenti/Uni/QF/Credit derivatives/Assignment/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb062ef0b6093a44/Documenti/Uni/QF/Credit derivatives/Assignment/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC56965-4D77-4C9C-9B0D-FBA4994D9807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{7EC56965-4D77-4C9C-9B0D-FBA4994D9807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C36F348A-E20F-4296-BB96-81103D3C3C0E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="2220" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{D28E9BA4-4557-4B46-B1A0-6510D1B70C36}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="CDS spread_2023" sheetId="1" r:id="rId1"/>
     <sheet name="CDS spread_2025" sheetId="3" r:id="rId2"/>
     <sheet name="swap curve" sheetId="4" r:id="rId3"/>
-    <sheet name="da ppt intensity" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="2" hidden="1">'swap curve'!$B$26:$B$31</definedName>
@@ -80,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
   <si>
     <t>Banco Santander</t>
   </si>
@@ -138,43 +137,15 @@
   <si>
     <t>s_errors</t>
   </si>
-  <si>
-    <t>nell'esempio del prof +6000 simulaz</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>Years</t>
-  </si>
-  <si>
-    <t>lambda constant</t>
-  </si>
-  <si>
-    <t>lambda</t>
-  </si>
-  <si>
-    <t>very simple model for average time to default</t>
-  </si>
-  <si>
-    <t>lgd</t>
-  </si>
-  <si>
-    <t>cds spread</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000000"/>
-    <numFmt numFmtId="165" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -209,13 +180,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
@@ -481,15 +445,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -546,20 +509,17 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
     <cellStyle name="Normale 2" xfId="1" xr:uid="{385CCBD7-8EE2-8843-A4CF-F79A189D92F5}"/>
-    <cellStyle name="Percentuale" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3241,321 +3201,4 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3251D3D7-B9F6-4F5A-88E4-883CBAE39037}">
-  <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2">
-        <v>0.6</v>
-      </c>
-      <c r="E2">
-        <f ca="1">AVERAGE(E4:E24)</f>
-        <v>11.618081919364133</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="41">
-        <f>B1/B2/10000</f>
-        <v>0.11666666666666667</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4">
-        <f t="shared" ref="E4:E24" ca="1" si="0">-1/B$4*LN(1-RAND())</f>
-        <v>7.6898499436340186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E5">
-        <f t="shared" ca="1" si="0"/>
-        <v>40.645862379130136</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E6">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.6729510876932</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7">
-        <f t="shared" ca="1" si="0"/>
-        <v>5.6415966398468473</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8" s="40">
-        <f t="shared" ref="B8:B19" si="1">EXP(-B$4*A8)</f>
-        <v>0.88988177098802379</v>
-      </c>
-      <c r="C8" s="40">
-        <f t="shared" ref="C8:C19" si="2">1-B8</f>
-        <v>0.11011822901197621</v>
-      </c>
-      <c r="E8">
-        <f t="shared" ca="1" si="0"/>
-        <v>2.9440293713383987</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9" s="40">
-        <f t="shared" si="1"/>
-        <v>0.79188956633678165</v>
-      </c>
-      <c r="C9" s="40">
-        <f t="shared" si="2"/>
-        <v>0.20811043366321835</v>
-      </c>
-      <c r="E9">
-        <f t="shared" ca="1" si="0"/>
-        <v>13.510764110644306</v>
-      </c>
-      <c r="G9">
-        <f>B8*EXP(-B$4)</f>
-        <v>0.79188956633678165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10" s="40">
-        <f t="shared" si="1"/>
-        <v>0.70468808971871344</v>
-      </c>
-      <c r="C10" s="40">
-        <f t="shared" si="2"/>
-        <v>0.29531191028128656</v>
-      </c>
-      <c r="E10">
-        <f t="shared" ca="1" si="0"/>
-        <v>6.145222471607469</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11" s="40">
-        <f t="shared" si="1"/>
-        <v>0.62708908527305607</v>
-      </c>
-      <c r="C11" s="40">
-        <f t="shared" si="2"/>
-        <v>0.37291091472694393</v>
-      </c>
-      <c r="E11">
-        <f t="shared" ca="1" si="0"/>
-        <v>6.3561062907295636</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>5</v>
-      </c>
-      <c r="B12" s="40">
-        <f t="shared" si="1"/>
-        <v>0.55803514577004709</v>
-      </c>
-      <c r="C12" s="40">
-        <f t="shared" si="2"/>
-        <v>0.44196485422995291</v>
-      </c>
-      <c r="E12">
-        <f t="shared" ca="1" si="0"/>
-        <v>22.16024748030609</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>6</v>
-      </c>
-      <c r="B13" s="40">
-        <f t="shared" si="1"/>
-        <v>0.49658530379140953</v>
-      </c>
-      <c r="C13" s="40">
-        <f t="shared" si="2"/>
-        <v>0.50341469620859047</v>
-      </c>
-      <c r="E13">
-        <f t="shared" ca="1" si="0"/>
-        <v>16.601289054500885</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>7</v>
-      </c>
-      <c r="B14" s="40">
-        <f t="shared" si="1"/>
-        <v>0.44190220958452531</v>
-      </c>
-      <c r="C14" s="40">
-        <f t="shared" si="2"/>
-        <v>0.55809779041547469</v>
-      </c>
-      <c r="E14">
-        <f t="shared" ca="1" si="0"/>
-        <v>12.580849474289762</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>8</v>
-      </c>
-      <c r="B15" s="40">
-        <f t="shared" si="1"/>
-        <v>0.39324072086859824</v>
-      </c>
-      <c r="C15" s="40">
-        <f t="shared" si="2"/>
-        <v>0.60675927913140182</v>
-      </c>
-      <c r="E15">
-        <f t="shared" ca="1" si="0"/>
-        <v>2.2983919839929854</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>9</v>
-      </c>
-      <c r="B16" s="40">
-        <f t="shared" si="1"/>
-        <v>0.34993774911115533</v>
-      </c>
-      <c r="C16" s="40">
-        <f t="shared" si="2"/>
-        <v>0.65006225088884473</v>
-      </c>
-      <c r="E16">
-        <f t="shared" ca="1" si="0"/>
-        <v>1.8389324096893649</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>10</v>
-      </c>
-      <c r="B17" s="40">
-        <f t="shared" si="1"/>
-        <v>0.31140322391459768</v>
-      </c>
-      <c r="C17" s="40">
-        <f t="shared" si="2"/>
-        <v>0.68859677608540237</v>
-      </c>
-      <c r="E17">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.23310422222173832</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>11</v>
-      </c>
-      <c r="B18" s="40">
-        <f t="shared" si="1"/>
-        <v>0.27711205238850228</v>
-      </c>
-      <c r="C18" s="40">
-        <f t="shared" si="2"/>
-        <v>0.72288794761149777</v>
-      </c>
-      <c r="E18">
-        <f t="shared" ca="1" si="0"/>
-        <v>6.7326226673215572</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>12</v>
-      </c>
-      <c r="B19" s="40">
-        <f t="shared" si="1"/>
-        <v>0.24659696394160649</v>
-      </c>
-      <c r="C19" s="40">
-        <f t="shared" si="2"/>
-        <v>0.75340303605839354</v>
-      </c>
-      <c r="E19">
-        <f t="shared" ca="1" si="0"/>
-        <v>8.7640769176984303</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E20">
-        <f t="shared" ca="1" si="0"/>
-        <v>7.3124989349437559</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E21">
-        <f t="shared" ca="1" si="0"/>
-        <v>20.072351314081175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E22">
-        <f t="shared" ca="1" si="0"/>
-        <v>4.1875102341488688</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E23">
-        <f t="shared" ca="1" si="0"/>
-        <v>8.7577073547007931</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E24">
-        <f t="shared" ca="1" si="0"/>
-        <v>26.83375596412748</v>
-      </c>
-      <c r="F24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>